--- a/WpfUI/Resources/Templates/DotnetNetworking/TestCase/Environment.xlsx
+++ b/WpfUI/Resources/Templates/DotnetNetworking/TestCase/Environment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FPTU\AI-AGENT-CAPSTONE\TestKitGenerator-Phase-3\RecordApp\Resources\ProjectResource\DotNetWebbased\Question\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnFall25\Code\Recorder_NetWorking\WpfUI\Resources\Templates\DotnetNetworking\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28909D2F-DBE0-4016-A5B9-E758A06F22F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E842A98E-5C16-4DAC-8DDC-5D03B28F7CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Key</t>
   </si>
@@ -34,30 +34,117 @@
     <t>Value</t>
   </si>
   <si>
+    <t>Environment_Type</t>
+  </si>
+  <si>
+    <t>dotnet</t>
+  </si>
+  <si>
     <t>Docker_Network</t>
   </si>
   <si>
+    <t>auto-grading-network</t>
+  </si>
+  <si>
+    <t>Code_Image_Name</t>
+  </si>
+  <si>
+    <t>fptuxaes/aes-dotnet8:latest</t>
+  </si>
+  <si>
+    <t>Code_Container_Name</t>
+  </si>
+  <si>
+    <t>auto-grading-dotnet-web-app</t>
+  </si>
+  <si>
+    <t>App_Type</t>
+  </si>
+  <si>
+    <t>Given_API_Container_Name</t>
+  </si>
+  <si>
+    <t>Given_API_File</t>
+  </si>
+  <si>
+    <t>Given_API_Internal_Port</t>
+  </si>
+  <si>
+    <t>Given_API_Host_Port</t>
+  </si>
+  <si>
+    <t>Database_Image_Name</t>
+  </si>
+  <si>
+    <t>mcr.microsoft.com/mssql/server:2019-latest</t>
+  </si>
+  <si>
+    <t>Database_Container_Name</t>
+  </si>
+  <si>
+    <t>auto-grading-sqlserver</t>
+  </si>
+  <si>
+    <t>Database_Container_Internal_Port</t>
+  </si>
+  <si>
+    <t>Database_Container_Host_Port</t>
+  </si>
+  <si>
+    <t>Database_Username</t>
+  </si>
+  <si>
+    <t>sa</t>
+  </si>
+  <si>
+    <t>Database_Password</t>
+  </si>
+  <si>
+    <t>Khanh@2721</t>
+  </si>
+  <si>
+    <t>Default_Database_Name</t>
+  </si>
+  <si>
+    <t>Default_Database_File_Path</t>
+  </si>
+  <si>
+    <t>Meta\database.sql</t>
+  </si>
+  <si>
+    <t>Runtimes_Folder</t>
+  </si>
+  <si>
+    <t>Meta\runtimes</t>
+  </si>
+  <si>
+    <t>ConnectDb_File</t>
+  </si>
+  <si>
+    <t>SignalR_Hub</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
     <t>create_network</t>
   </si>
   <si>
+    <t>create docker network</t>
+  </si>
+  <si>
     <t>create_sqlserver_container</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>create docker network</t>
-  </si>
-  <si>
     <t>deploy sqlserver image as container</t>
   </si>
   <si>
@@ -100,103 +187,22 @@
     <t>validate_content</t>
   </si>
   <si>
-    <t>Environment_Type</t>
-  </si>
-  <si>
-    <t>dotnet</t>
-  </si>
-  <si>
-    <t>auto-grading-network</t>
-  </si>
-  <si>
-    <t>Code_Image_Name</t>
-  </si>
-  <si>
-    <t>Code_Container_Name</t>
-  </si>
-  <si>
-    <t>Code_Container_Internal_Port</t>
-  </si>
-  <si>
-    <t>Code_Container_Host_Port</t>
-  </si>
-  <si>
-    <t>App_Type</t>
-  </si>
-  <si>
-    <t>Given_API_Container_Name</t>
-  </si>
-  <si>
-    <t>Given_API_File</t>
-  </si>
-  <si>
-    <t>Given_API_Internal_Port</t>
-  </si>
-  <si>
-    <t>Given_API_Host_Port</t>
-  </si>
-  <si>
-    <t>Database_Image_Name</t>
-  </si>
-  <si>
-    <t>mcr.microsoft.com/mssql/server:2019-latest</t>
-  </si>
-  <si>
-    <t>Database_Container_Name</t>
-  </si>
-  <si>
-    <t>auto-grading-sqlserver</t>
-  </si>
-  <si>
-    <t>Database_Container_Internal_Port</t>
-  </si>
-  <si>
-    <t>Database_Container_Host_Port</t>
-  </si>
-  <si>
-    <t>Database_Username</t>
-  </si>
-  <si>
-    <t>sa</t>
-  </si>
-  <si>
-    <t>Database_Password</t>
-  </si>
-  <si>
-    <t>Default_Database_Name</t>
-  </si>
-  <si>
-    <t>Default_Database_File_Path</t>
-  </si>
-  <si>
-    <t>Meta\database.sql</t>
-  </si>
-  <si>
-    <t>Runtimes_Folder</t>
-  </si>
-  <si>
-    <t>Meta\runtimes</t>
-  </si>
-  <si>
-    <t>ConnectDb_File</t>
-  </si>
-  <si>
-    <t>SignalR_Hub</t>
-  </si>
-  <si>
-    <t>SamplePE</t>
-  </si>
-  <si>
-    <t>webapp</t>
-  </si>
-  <si>
-    <t>fptuxaes/aes-dotnet8:latest</t>
-  </si>
-  <si>
-    <t>auto-grading-dotnet-web-app</t>
-  </si>
-  <si>
-    <t>Khanh@2721</t>
+    <t>PE_PRN_Sum25B5_WA</t>
+  </si>
+  <si>
+    <t>Port Middleware</t>
+  </si>
+  <si>
+    <t>Port Server</t>
+  </si>
+  <si>
+    <t>Console</t>
+  </si>
+  <si>
+    <t>Given</t>
+  </si>
+  <si>
+    <t>Meta\Given</t>
   </si>
 </sst>
 </file>
@@ -354,28 +360,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -402,26 +408,26 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -753,16 +759,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="30.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -770,173 +777,181 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="B6" s="9">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>30</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="B7" s="10">
         <v>8081</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B9" s="10"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B10" s="11"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B11" s="11"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B12" s="12"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B15" s="13">
         <v>1433</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B16" s="13">
         <v>1434</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="13"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="15"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="13"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1" xr:uid="{52CBEDC5-FE9B-46A4-A397-A24014C8CA7B}"/>
+    <hyperlink ref="B18" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -945,107 +960,107 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A83C95-3B80-4231-A2A3-554283AC2A02}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="37.21875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="37.1796875" style="7" customWidth="1"/>
     <col min="3" max="3" width="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="18"/>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="18"/>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="18"/>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="18"/>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4"/>
     </row>
